--- a/contacts/organizations.xlsx
+++ b/contacts/organizations.xlsx
@@ -75,11 +75,11 @@
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="34" customWidth="1"/>
-    <col min="5" max="5" width="34" customWidth="1"/>
+    <col min="5" max="5" width="38" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="44" customWidth="1"/>
+    <col min="9" max="9" width="58" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -129,7 +129,54 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr" s="0">
+        <is>
+          <t>ORG-2026-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr" s="0">
+        <is>
+          <t>ועד בית בית לחם 49</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr" s="0">
+        <is>
+          <t>ועד בית</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr" s="0">
+        <is>
+          <t>Бейт Лехем 49 / בית לחם 49</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr" s="0">
+        <is>
+          <t>CONTACT-2026-001 — אבי לוי</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr" s="0">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr" s="0">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr" s="0">
+        <is>
+          <t>Связан с CASE-2026-001: канализация между домами, оплаченная ими работа, хотят разделить цену.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I1"/>
+  <autoFilter ref="A1:I2"/>
 </worksheet>
 </file>
--- a/contacts/organizations.xlsx
+++ b/contacts/organizations.xlsx
@@ -152,7 +152,7 @@
       </c>
       <c r="E2" t="inlineStr" s="0">
         <is>
-          <t>CONTACT-2026-001 — אבי לוי</t>
+          <t>CONTACT-2026-001 — אבי לוי; CONTACT-2026-002 — עאיד אבו סריה</t>
         </is>
       </c>
       <c r="F2" t="inlineStr" s="0">
@@ -167,12 +167,12 @@
       </c>
       <c r="H2" t="inlineStr" s="0">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="I2" t="inlineStr" s="0">
         <is>
-          <t>Связан с CASE-2026-001: канализация между домами, оплаченная ими работа, хотят разделить цену.</t>
+          <t>Связан с CASE-2026-001: канализация между домами; указан руководитель ועד בית עאיד אבו סריה. Ожидаются документы по личной оплате 472 ILS и работе инсталлятора.</t>
         </is>
       </c>
     </row>
